--- a/uniclaw统计结果.xlsx
+++ b/uniclaw统计结果.xlsx
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>2026.06.05</t>
+  </si>
+  <si>
+    <t>陈老师单独贡献的tokens</t>
   </si>
   <si>
     <t>2026.06.06</t>
@@ -262,6 +265,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>90097</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="14560550" cy="2148278"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="图片 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -845,7 +878,9 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
@@ -876,7 +911,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>10006792</v>
@@ -926,7 +961,7 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>10229232</v>
@@ -976,7 +1011,7 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>33804986</v>
@@ -1026,7 +1061,7 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>143428163</v>
@@ -1076,7 +1111,7 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>93749333</v>
@@ -1126,7 +1161,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>136449733</v>
@@ -1174,13 +1209,19 @@
       <c r="AM12" s="9"/>
       <c r="AN12" s="9"/>
     </row>
-    <row r="13" ht="14.002500000000003" customHeight="1">
+    <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="B13" s="10" t="n">
+        <v>131155138</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>21</v>
+      </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -1218,13 +1259,19 @@
       <c r="AM13" s="10"/>
       <c r="AN13" s="10"/>
     </row>
-    <row r="14" ht="14.002500000000003" customHeight="1">
+    <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="9" t="n">
+        <v>71848416</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -1262,13 +1309,19 @@
       <c r="AM14" s="9"/>
       <c r="AN14" s="9"/>
     </row>
-    <row r="15" ht="14.002500000000003" customHeight="1">
+    <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="B15" s="10" t="n">
+        <v>86543686</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -1306,13 +1359,19 @@
       <c r="AM15" s="10"/>
       <c r="AN15" s="10"/>
     </row>
-    <row r="16" ht="14.002500000000003" customHeight="1">
+    <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="9" t="n">
+        <v>202828198</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -1352,7 +1411,7 @@
     </row>
     <row r="17" ht="14.002500000000003" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -1396,7 +1455,7 @@
     </row>
     <row r="18" ht="14.002500000000003" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1440,7 +1499,7 @@
     </row>
     <row r="19" ht="14.002500000000003" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1484,7 +1543,7 @@
     </row>
     <row r="20" ht="14.002500000000003" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1528,7 +1587,7 @@
     </row>
     <row r="21" ht="14.002500000000003" customHeight="1">
       <c r="A21" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1572,7 +1631,7 @@
     </row>
     <row r="22" ht="14.002500000000003" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1616,7 +1675,7 @@
     </row>
     <row r="23" ht="14.002500000000003" customHeight="1">
       <c r="A23" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -1660,7 +1719,7 @@
     </row>
     <row r="24" ht="14.002500000000003" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1704,7 +1763,7 @@
     </row>
     <row r="25" ht="14.002500000000003" customHeight="1">
       <c r="A25" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1748,7 +1807,7 @@
     </row>
     <row r="26" ht="14.002500000000003" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1792,7 +1851,7 @@
     </row>
     <row r="27" ht="14.002500000000003" customHeight="1">
       <c r="A27" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1836,7 +1895,7 @@
     </row>
     <row r="28" ht="14.002500000000003" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1880,7 +1939,7 @@
     </row>
     <row r="29" ht="14.002500000000003" customHeight="1">
       <c r="A29" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -1924,7 +1983,7 @@
     </row>
     <row r="30" ht="14.002500000000003" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1968,7 +2027,7 @@
     </row>
     <row r="31" ht="14.002500000000003" customHeight="1">
       <c r="A31" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -2181,13 +2240,13 @@
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="9"/>
       <c r="B36" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -2232,15 +2291,15 @@
       </c>
       <c r="B37" s="10" t="n">
         <f>SUM(B2:B31)</f>
-        <v>724919609</v>
+        <v>1217295047</v>
       </c>
       <c r="C37" s="10" t="n">
         <f>SUM(C2:C31)</f>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D37" s="10" t="n">
         <f>SUM(D2:D31)</f>
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
@@ -9128,5 +9187,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/uniclaw统计结果.xlsx
+++ b/uniclaw统计结果.xlsx
@@ -272,11 +272,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>90097</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="14560550" cy="2148278"/>
+    <xdr:ext cx="13370359" cy="2290561"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="图片 1"/>
@@ -1409,13 +1409,19 @@
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
     </row>
-    <row r="17" ht="14.002500000000003" customHeight="1">
+    <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="B17" s="10" t="n">
+        <v>198158037</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>22</v>
+      </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -1453,13 +1459,19 @@
       <c r="AM17" s="10"/>
       <c r="AN17" s="10"/>
     </row>
-    <row r="18" ht="14.002500000000003" customHeight="1">
+    <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="9" t="n">
+        <v>90254741</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>22</v>
+      </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -2291,15 +2303,15 @@
       </c>
       <c r="B37" s="10" t="n">
         <f>SUM(B2:B31)</f>
-        <v>1217295047</v>
+        <v>1505707825</v>
       </c>
       <c r="C37" s="10" t="n">
         <f>SUM(C2:C31)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D37" s="10" t="n">
         <f>SUM(D2:D31)</f>
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>

--- a/uniclaw统计结果.xlsx
+++ b/uniclaw统计结果.xlsx
@@ -271,12 +271,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="13370359" cy="2290561"/>
+    <xdr:ext cx="13138195" cy="3313888"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="图片 1"/>
@@ -1509,13 +1509,19 @@
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
     </row>
-    <row r="19" ht="14.002500000000003" customHeight="1">
+    <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="B19" s="10" t="n">
+        <v>49081696</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>20</v>
+      </c>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -1553,13 +1559,19 @@
       <c r="AM19" s="10"/>
       <c r="AN19" s="10"/>
     </row>
-    <row r="20" ht="14.002500000000003" customHeight="1">
+    <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="9" t="n">
+        <v>15351434</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -1597,13 +1609,19 @@
       <c r="AM20" s="9"/>
       <c r="AN20" s="9"/>
     </row>
-    <row r="21" ht="14.002500000000003" customHeight="1">
+    <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="B21" s="10" t="n">
+        <v>136942985</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -1641,13 +1659,19 @@
       <c r="AM21" s="10"/>
       <c r="AN21" s="10"/>
     </row>
-    <row r="22" ht="14.002500000000003" customHeight="1">
+    <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
+      <c r="B22" s="9" t="n">
+        <v>105239994</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -1685,13 +1709,19 @@
       <c r="AM22" s="9"/>
       <c r="AN22" s="9"/>
     </row>
-    <row r="23" ht="14.002500000000003" customHeight="1">
+    <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="10" t="n">
+        <v>78912018</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>23</v>
+      </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -1729,13 +1759,19 @@
       <c r="AM23" s="10"/>
       <c r="AN23" s="10"/>
     </row>
-    <row r="24" ht="14.002500000000003" customHeight="1">
+    <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="9" t="n">
+        <v>90603420</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>22</v>
+      </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -1773,13 +1809,19 @@
       <c r="AM24" s="9"/>
       <c r="AN24" s="9"/>
     </row>
-    <row r="25" ht="14.002500000000003" customHeight="1">
+    <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="B25" s="10" t="n">
+        <v>206548186</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>26</v>
+      </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -1817,13 +1859,19 @@
       <c r="AM25" s="10"/>
       <c r="AN25" s="10"/>
     </row>
-    <row r="26" ht="14.002500000000003" customHeight="1">
+    <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="B26" s="9" t="n">
+        <v>223061885</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -1861,13 +1909,19 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="9"/>
     </row>
-    <row r="27" ht="14.002500000000003" customHeight="1">
+    <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="B27" s="10" t="n">
+        <v>54143092</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>19</v>
+      </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1905,13 +1959,19 @@
       <c r="AM27" s="10"/>
       <c r="AN27" s="10"/>
     </row>
-    <row r="28" ht="14.002500000000003" customHeight="1">
+    <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="B28" s="9" t="n">
+        <v>30374887</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -1949,13 +2009,19 @@
       <c r="AM28" s="9"/>
       <c r="AN28" s="9"/>
     </row>
-    <row r="29" ht="14.002500000000003" customHeight="1">
+    <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="B29" s="10" t="n">
+        <v>95063362</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
@@ -1993,13 +2059,19 @@
       <c r="AM29" s="10"/>
       <c r="AN29" s="10"/>
     </row>
-    <row r="30" ht="14.002500000000003" customHeight="1">
+    <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="9" t="n">
+        <v>81533183</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>19</v>
+      </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -2037,13 +2109,19 @@
       <c r="AM30" s="9"/>
       <c r="AN30" s="9"/>
     </row>
-    <row r="31" ht="14.002500000000003" customHeight="1">
+    <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="B31" s="10" t="n">
+        <v>157869044</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>21</v>
+      </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
@@ -2303,15 +2381,15 @@
       </c>
       <c r="B37" s="10" t="n">
         <f>SUM(B2:B31)</f>
-        <v>1505707825</v>
+        <v>2830433011</v>
       </c>
       <c r="C37" s="10" t="n">
         <f>SUM(C2:C31)</f>
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D37" s="10" t="n">
         <f>SUM(D2:D31)</f>
-        <v>258</v>
+        <v>456</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
